--- a/data/trans_dic/P41C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P41C_R-Edad-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo</t>
+          <t>Población con dificultades para tener un embarazo (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 12,54</t>
+          <t>0,9; 12,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,26</t>
+          <t>2,2; 9,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 9,17</t>
+          <t>2,1; 8,67</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 9,63</t>
+          <t>2,5; 8,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,51</t>
+          <t>3,29; 8,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,42</t>
+          <t>3,43; 7,65</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,3</t>
+          <t>0,3; 6,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,6</t>
+          <t>2,7; 6,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,49</t>
+          <t>1,05; 5,56</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>65-74</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -822,137 +822,35 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,15; 5,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,08; 5,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,23; 4,79</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 5,04</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3,03; 5,73</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2,09; 4,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -965,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -978,7 +876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo</t>
+          <t>Población con dificultades para tener un embarazo (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4126</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2666</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3273</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1240; 16977</t>
+          <t>1222; 17579</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3086; 13562</t>
+          <t>3220; 14048</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6185; 25832</t>
+          <t>5922; 24437</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4915; 19037</t>
+          <t>4931; 17160</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7340; 18456</t>
+          <t>7126; 18629</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14579; 30727</t>
+          <t>14210; 31682</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1637; 28645</t>
+          <t>1371; 29487</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6188; 16240</t>
+          <t>6645; 16332</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7109; 38493</t>
+          <t>7336; 38961</t>
         </is>
       </c>
     </row>
@@ -1375,24 +1273,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1630</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1093</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1377</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>65-74</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1402,17 +1300,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26491</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29437</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55929</t>
         </is>
       </c>
     </row>
@@ -1448,183 +1346,35 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10115; 44032</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21409; 40083</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35191; 75386</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>26491</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>29437</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>55929</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>10962; 44316</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>21071; 39850</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>32890; 75740</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A27"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P41C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P41C_R-Edad-trans_dic.xlsx
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 12,98</t>
+          <t>0,79; 12,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,59</t>
+          <t>2,03; 8,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 8,67</t>
+          <t>2,32; 9,09</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,68</t>
+          <t>2,56; 8,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,59</t>
+          <t>3,11; 8,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,65</t>
+          <t>3,59; 7,51</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,48</t>
+          <t>2,49; 8,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,63</t>
+          <t>2,6; 6,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,56</t>
+          <t>3,05; 6,6</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,01</t>
+          <t>2,64; 6,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,77</t>
+          <t>2,98; 5,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,79</t>
+          <t>3,19; 5,41</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>13880</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1222; 17579</t>
+          <t>1192; 18640</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3220; 14048</t>
+          <t>3309; 13915</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5922; 24437</t>
+          <t>7280; 28527</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1104,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>24065</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4931; 17160</t>
+          <t>5644; 19271</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7126; 18629</t>
+          <t>7697; 19923</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14210; 31682</t>
+          <t>16785; 35139</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>22380</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1371; 29487</t>
+          <t>5747; 20067</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6645; 16332</t>
+          <t>6973; 16841</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7336; 38961</t>
+          <t>15229; 32965</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>31769</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>60325</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10115; 44032</t>
+          <t>18345; 45806</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21409; 40083</t>
+          <t>23090; 42269</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35191; 75386</t>
+          <t>46801; 79563</t>
         </is>
       </c>
     </row>
